--- a/outputs/churn_model_comparison.xlsx
+++ b/outputs/churn_model_comparison.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="model_comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="model_comparison" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +514,7 @@
         <v>0.5775862068965517</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4743457521716753</v>
+        <v>0.4743457521716754</v>
       </c>
       <c r="F2" t="n">
         <v>0.9303990252817546</v>
@@ -523,7 +523,7 @@
         <v>0.9595044610253826</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5380230930245646</v>
+        <v>0.5380230930245647</v>
       </c>
       <c r="I2" t="n">
         <v>0.9454545454545454</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{"threshold": 0.5380230930245646, "precision": 0.9454545454545454, "recall": 0.7761194029850746, "f2": 0.804953560371517, "urgent_count": 55.0}</t>
+          <t>{"threshold": 0.5380230930245647, "precision": 0.9454545454545454, "recall": 0.7761194029850746, "f2": 0.804953560371517, "urgent_count": 55.0}</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
         <v>0.5775862068965517</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4427200555801392</v>
+        <v>0.4426343441009521</v>
       </c>
       <c r="F3" t="n">
         <v>0.9240024367956139</v>
@@ -577,7 +577,7 @@
         <v>0.9434816735108426</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5071833729743958</v>
+        <v>0.5072267055511475</v>
       </c>
       <c r="I3" t="n">
         <v>0.9433962264150944</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{"threshold": 0.5071833729743958, "precision": 0.9433962264150944, "recall": 0.746268656716418, "f2": 0.778816199376947, "urgent_count": 53.0}</t>
+          <t>{"threshold": 0.5072267055511475, "precision": 0.9433962264150944, "recall": 0.746268656716418, "f2": 0.778816199376947, "urgent_count": 53.0}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>0.5775862068965517</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4639706240851924</v>
+        <v>0.4639706240851922</v>
       </c>
       <c r="F4" t="n">
         <v>0.7998781602193117</v>
@@ -656,7 +656,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{"threshold": 0.28311307599309066, "precision": 0.8157894736842105, "recall": 0.9253731343283582, "f2": 0.9011627906976745, "urgent_count": 76.0}</t>
+          <t>{"threshold": 0.2831130759930907, "precision": 0.8157894736842105, "recall": 0.9253731343283582, "f2": 0.9011627906976745, "urgent_count": 76.0}</t>
         </is>
       </c>
     </row>
